--- a/individual_Tests/close/close_test_results.xlsx
+++ b/individual_Tests/close/close_test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge\Desktop\Masters\Tests\initial_tests\individual_Tests\close\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF680F0-B7C3-429B-9C12-91DE2AF132E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9C7244-65D4-4F3B-8A6B-D7C6C7049559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
